--- a/data/sars/alaska/tables/Alaska_2023_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2023_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E67A4A-9AEB-0A4E-B6A5-B9E9D786D75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8BF4AF-B2B4-AF4A-9D51-4B6D2B46CD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{BC4D90C3-6FB5-1249-8F5A-B0E44F1798BA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="103">
   <si>
     <t>S</t>
   </si>
@@ -260,30 +260,6 @@
     <t>Steller sea lion (Western)</t>
   </si>
   <si>
-    <t>73,211 (49,837 in U.S. only)</t>
-  </si>
-  <si>
-    <t>36,308 (U.S. only)</t>
-  </si>
-  <si>
-    <t>439 (299 for U.S. only)</t>
-  </si>
-  <si>
-    <t>2,178 (U.S. only)</t>
-  </si>
-  <si>
-    <t>3.4 (0.2 for U.S. waters)</t>
-  </si>
-  <si>
-    <t>267 (267 in U.S. only)</t>
-  </si>
-  <si>
-    <t>92.3 (U.S. only)</t>
-  </si>
-  <si>
-    <t>5.82 (0.06 in U.S. waters)</t>
-  </si>
-  <si>
     <t>N/A (New SAR in 2022)</t>
   </si>
   <si>
@@ -351,6 +327,33 @@
   </si>
   <si>
     <t>Harbor seal (Clarence Strait)</t>
+  </si>
+  <si>
+    <t>n_min_notes</t>
+  </si>
+  <si>
+    <t>49,837 in U.S. only</t>
+  </si>
+  <si>
+    <t>U.S. only</t>
+  </si>
+  <si>
+    <t>pbr_notes</t>
+  </si>
+  <si>
+    <t>299 for U.S. only</t>
+  </si>
+  <si>
+    <t>0.2 for U.S. waters</t>
+  </si>
+  <si>
+    <t>sim_total_notes</t>
+  </si>
+  <si>
+    <t>267 in U.S. only</t>
+  </si>
+  <si>
+    <t>0.06 in U.S. waters</t>
   </si>
 </sst>
 </file>
@@ -1247,28 +1250,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B59532-4ECC-9545-91E4-1301B4906CAD}">
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="76.5" style="1" customWidth="1"/>
     <col min="3" max="4" width="10.83203125" style="1"/>
-    <col min="5" max="5" width="25.5" style="1" customWidth="1"/>
-    <col min="6" max="7" width="10.83203125" style="1"/>
-    <col min="8" max="8" width="25.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" style="1" customWidth="1"/>
-    <col min="12" max="13" width="10.83203125" style="1"/>
-    <col min="14" max="14" width="22.33203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="135.83203125" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="10.83203125" style="1"/>
+    <col min="5" max="6" width="25.5" style="1" customWidth="1"/>
+    <col min="7" max="8" width="10.83203125" style="1"/>
+    <col min="9" max="10" width="25.6640625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="30.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16.1640625" style="1" customWidth="1"/>
+    <col min="15" max="16" width="10.83203125" style="1"/>
+    <col min="17" max="17" width="22.33203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="135.83203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>55</v>
@@ -1280,130 +1283,157 @@
         <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3">
         <v>49837</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" s="3">
+        <v>73211</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="1">
         <v>0.12</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>0.1</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="I2" s="1">
+        <v>439</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K2" s="1">
+        <v>267</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M2" s="1">
         <v>39</v>
       </c>
-      <c r="K2">
+      <c r="N2">
         <v>218</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="1">
+      <c r="Q2" s="1">
         <v>2023</v>
       </c>
-      <c r="O2" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R2" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3">
         <v>36308</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" s="3">
+        <v>36308</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="1">
         <v>0.12</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>1</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="I3" s="3">
+        <v>2178</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="1">
+        <v>92.3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3" s="1">
         <v>20.5</v>
       </c>
-      <c r="K3">
+      <c r="N3">
         <v>11</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="1">
+      <c r="Q3" s="1">
         <v>2023</v>
       </c>
-      <c r="O3" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R3" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C4" s="3">
         <v>626618</v>
@@ -1414,43 +1444,45 @@
       <c r="E4" s="3">
         <v>530376</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>0.5</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>11403</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="3"/>
+      <c r="K4" s="1">
         <v>373</v>
       </c>
-      <c r="J4" s="1">
+      <c r="M4" s="1">
         <v>3.5</v>
       </c>
-      <c r="K4">
+      <c r="N4">
         <v>360</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1" t="s">
+      <c r="O4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="1">
+      <c r="Q4" s="1">
         <v>2021</v>
       </c>
-      <c r="O4" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R4" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C5" s="3">
         <v>5588</v>
@@ -1458,41 +1490,42 @@
       <c r="E5" s="3">
         <v>5366</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
         <v>0.12</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>0.3</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>97</v>
       </c>
-      <c r="I5" s="1">
+      <c r="K5" s="1">
         <v>90</v>
       </c>
-      <c r="J5" s="1">
+      <c r="M5" s="1">
         <v>0.4</v>
       </c>
-      <c r="K5">
+      <c r="N5">
         <v>90</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="1">
+      <c r="P5" s="1">
         <v>2018</v>
       </c>
-      <c r="N5" s="1">
+      <c r="Q5" s="1">
         <v>2019</v>
       </c>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C6" s="1">
         <v>229</v>
@@ -1500,43 +1533,43 @@
       <c r="E6" s="1">
         <v>229</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>0.12</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>0.5</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>7</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M6" s="1">
+      <c r="P6" s="1">
         <v>2018</v>
       </c>
-      <c r="N6" s="1">
+      <c r="Q6" s="1">
         <v>2019</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R6" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C7" s="3">
         <v>44781</v>
@@ -1545,41 +1578,43 @@
       <c r="E7" s="3">
         <v>38254</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
         <v>0.12</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>0.7</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>1607</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="3"/>
+      <c r="K7" s="1">
         <v>20</v>
       </c>
-      <c r="J7" s="1">
+      <c r="M7" s="1">
         <v>3.8</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>15</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="1">
+      <c r="P7" s="1">
         <v>2017</v>
       </c>
-      <c r="N7" s="1">
+      <c r="Q7" s="1">
         <v>2019</v>
       </c>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R7" s="6"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3">
         <v>8677</v>
@@ -1588,41 +1623,42 @@
       <c r="E8" s="3">
         <v>7609</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
         <v>0.12</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>0.5</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>228</v>
       </c>
-      <c r="I8" s="1">
+      <c r="K8" s="1">
         <v>38</v>
       </c>
-      <c r="J8" s="1">
+      <c r="M8" s="1">
         <v>0.3</v>
       </c>
-      <c r="K8">
+      <c r="N8">
         <v>37</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="O8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="1">
+      <c r="P8" s="1">
         <v>2017</v>
       </c>
-      <c r="N8" s="1">
+      <c r="Q8" s="1">
         <v>2019</v>
       </c>
-      <c r="O8" s="6"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R8" s="6"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3">
         <v>26448</v>
@@ -1631,41 +1667,42 @@
       <c r="E9" s="3">
         <v>22351</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
         <v>0.12</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>0.7</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>939</v>
       </c>
-      <c r="I9" s="1">
+      <c r="K9" s="1">
         <v>127</v>
       </c>
-      <c r="J9" s="1">
+      <c r="M9" s="1">
         <v>1.2</v>
       </c>
-      <c r="K9">
+      <c r="N9">
         <v>126</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M9" s="1">
+      <c r="P9" s="1">
         <v>2017</v>
       </c>
-      <c r="N9" s="1">
+      <c r="Q9" s="1">
         <v>2019</v>
       </c>
-      <c r="O9" s="6"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R9" s="6"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C10" s="3">
         <v>44756</v>
@@ -1674,41 +1711,43 @@
       <c r="E10" s="3">
         <v>41776</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
         <v>0.12</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>0.5</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1253</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="3"/>
+      <c r="K10" s="1">
         <v>413</v>
       </c>
-      <c r="J10" s="1">
+      <c r="M10" s="1">
         <v>24</v>
       </c>
-      <c r="K10">
+      <c r="N10">
         <v>387</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M10" s="1">
+      <c r="P10" s="1">
         <v>2015</v>
       </c>
-      <c r="N10" s="1">
+      <c r="Q10" s="1">
         <v>2019</v>
       </c>
-      <c r="O10" s="6"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R10" s="6"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3">
         <v>28411</v>
@@ -1717,41 +1756,42 @@
       <c r="E11" s="3">
         <v>26907</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
         <v>0.12</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>0.5</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>807</v>
       </c>
-      <c r="I11" s="1">
+      <c r="K11" s="1">
         <v>107</v>
       </c>
-      <c r="J11" s="1">
+      <c r="M11" s="1">
         <v>2.5</v>
       </c>
-      <c r="K11">
+      <c r="N11">
         <v>104</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M11" s="1">
+      <c r="P11" s="1">
         <v>2018</v>
       </c>
-      <c r="N11" s="1">
+      <c r="Q11" s="1">
         <v>2019</v>
       </c>
-      <c r="O11" s="6"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R11" s="6"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3">
         <v>7455</v>
@@ -1760,41 +1800,42 @@
       <c r="E12" s="3">
         <v>6680</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
         <v>0.12</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>0.3</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>120</v>
       </c>
-      <c r="I12" s="1">
+      <c r="K12" s="1">
         <v>104</v>
       </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>104</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M12" s="1">
+      <c r="P12" s="1">
         <v>2017</v>
       </c>
-      <c r="N12" s="1">
+      <c r="Q12" s="1">
         <v>2019</v>
       </c>
-      <c r="O12" s="6"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3">
         <v>13388</v>
@@ -1803,41 +1844,42 @@
       <c r="E13" s="3">
         <v>11867</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
         <v>0.12</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>0.3</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>214</v>
       </c>
-      <c r="I13" s="1">
+      <c r="K13" s="1">
         <v>50</v>
       </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13">
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>50</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M13" s="1">
+      <c r="P13" s="1">
         <v>2016</v>
       </c>
-      <c r="N13" s="1">
+      <c r="Q13" s="1">
         <v>2019</v>
       </c>
-      <c r="O13" s="6"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C14" s="3">
         <v>13289</v>
@@ -1846,41 +1888,42 @@
       <c r="E14" s="3">
         <v>11883</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
         <v>0.12</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>0.5</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>356</v>
       </c>
-      <c r="I14" s="1">
+      <c r="K14" s="1">
         <v>77</v>
       </c>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14">
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14">
         <v>77</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="O14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M14" s="1">
+      <c r="P14" s="1">
         <v>2015</v>
       </c>
-      <c r="N14" s="1">
+      <c r="Q14" s="1">
         <v>2019</v>
       </c>
-      <c r="O14" s="6"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R14" s="6"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C15" s="3">
         <v>23478</v>
@@ -1889,41 +1932,42 @@
       <c r="E15" s="3">
         <v>21453</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
         <v>0.12</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>0.5</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>644</v>
       </c>
-      <c r="I15" s="1">
+      <c r="K15" s="1">
         <v>69</v>
       </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15">
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15">
         <v>69</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M15" s="1">
+      <c r="P15" s="1">
         <v>2015</v>
       </c>
-      <c r="N15" s="1">
+      <c r="Q15" s="1">
         <v>2019</v>
       </c>
-      <c r="O15" s="6"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R15" s="6"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C16" s="3">
         <v>27659</v>
@@ -1932,41 +1976,42 @@
       <c r="E16" s="3">
         <v>24854</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
         <v>0.12</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>0.5</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>746</v>
       </c>
-      <c r="I16" s="1">
+      <c r="K16" s="1">
         <v>40</v>
       </c>
-      <c r="J16" s="1">
-        <v>0</v>
-      </c>
-      <c r="K16">
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>40</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="O16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M16" s="1">
+      <c r="P16" s="1">
         <v>2015</v>
       </c>
-      <c r="N16" s="1">
+      <c r="Q16" s="1">
         <v>2019</v>
       </c>
-      <c r="O16" s="6"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R16" s="6"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C17" s="3">
         <v>461625</v>
@@ -1975,111 +2020,116 @@
       <c r="E17" s="3">
         <v>423237</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
         <v>0.12</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>1</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25394</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3"/>
+      <c r="K17" s="3">
         <v>5254</v>
       </c>
-      <c r="J17" s="1">
+      <c r="L17" s="3"/>
+      <c r="M17" s="1">
         <v>1</v>
       </c>
-      <c r="K17" s="5">
+      <c r="N17" s="5">
         <v>5253</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N17" s="1">
+      <c r="Q17" s="1">
         <v>2020</v>
       </c>
-      <c r="O17" s="6"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R17" s="6"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="1">
+        <v>76</v>
+      </c>
+      <c r="G18" s="1">
         <v>0.12</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>0.5</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>6709</v>
       </c>
-      <c r="J18" s="1">
+      <c r="L18" s="3"/>
+      <c r="M18" s="1">
         <v>1.8</v>
       </c>
-      <c r="K18" s="5">
+      <c r="N18" s="5">
         <v>6707</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1" t="s">
+      <c r="O18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N18" s="1">
+      <c r="Q18" s="1">
         <v>2020</v>
       </c>
-      <c r="O18" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R18" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="1">
+        <v>76</v>
+      </c>
+      <c r="G19" s="1">
         <v>0.12</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>0.5</v>
       </c>
-      <c r="I19" s="3">
+      <c r="K19" s="3">
         <v>6459</v>
       </c>
-      <c r="J19" s="1">
+      <c r="L19" s="3"/>
+      <c r="M19" s="1">
         <v>5</v>
       </c>
-      <c r="K19" s="5">
+      <c r="N19" s="5">
         <v>6454</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1" t="s">
+      <c r="O19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N19" s="1">
+      <c r="Q19" s="1">
         <v>2020</v>
       </c>
-      <c r="O19" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R19" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C20" s="3">
         <v>184697</v>
@@ -2087,41 +2137,43 @@
       <c r="E20" s="3">
         <v>163086</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
         <v>0.12</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>1</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9785</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="3"/>
+      <c r="K20" s="1">
         <v>163</v>
       </c>
-      <c r="J20" s="1">
+      <c r="M20" s="1">
         <v>0.9</v>
       </c>
-      <c r="K20">
+      <c r="N20">
         <v>162</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="O20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="P20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="1">
+      <c r="Q20" s="1">
         <v>2020</v>
       </c>
-      <c r="O20" s="6"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R20" s="6"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C21" s="3">
         <v>39258</v>
@@ -2132,41 +2184,41 @@
       <c r="E21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>0.04</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>1</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I21" s="1">
+      <c r="K21" s="1">
         <v>104</v>
       </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
-      <c r="K21">
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21">
         <v>104</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M21" s="1">
+      <c r="P21" s="1">
         <v>1992</v>
       </c>
-      <c r="N21" s="1">
+      <c r="Q21" s="1">
         <v>2020</v>
       </c>
-      <c r="O21" s="6"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R21" s="6"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C22" s="3">
         <v>13305</v>
@@ -2177,41 +2229,42 @@
       <c r="E22" s="3">
         <v>8875</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
         <v>0.04</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>1</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>178</v>
       </c>
-      <c r="I22" s="1">
+      <c r="K22" s="1">
         <v>56</v>
       </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22">
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22">
         <v>56</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M22" s="1">
+      <c r="P22" s="1">
         <v>2017</v>
       </c>
-      <c r="N22" s="1">
+      <c r="Q22" s="1">
         <v>2020</v>
       </c>
-      <c r="O22" s="6"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R22" s="6"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C23" s="3">
         <v>12269</v>
@@ -2222,41 +2275,42 @@
       <c r="E23" s="3">
         <v>11112</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>1</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>267</v>
       </c>
-      <c r="I23" s="1">
+      <c r="K23" s="1">
         <v>227</v>
       </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23">
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23">
         <v>227</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M23" s="1">
+      <c r="P23" s="1">
         <v>2017</v>
       </c>
-      <c r="N23" s="1">
+      <c r="Q23" s="1">
         <v>2022</v>
       </c>
-      <c r="O23" s="6"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R23" s="6"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C24" s="3">
         <v>2040</v>
@@ -2267,41 +2321,42 @@
       <c r="E24" s="3">
         <v>1645</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
         <v>0.04</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>1</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <v>33</v>
       </c>
-      <c r="I24" s="1">
+      <c r="K24" s="1">
         <v>19</v>
       </c>
-      <c r="J24" s="1">
-        <v>0</v>
-      </c>
-      <c r="K24">
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24">
         <v>19</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M24" s="1">
+      <c r="P24" s="1">
         <v>2016</v>
       </c>
-      <c r="N24" s="1">
+      <c r="Q24" s="1">
         <v>2020</v>
       </c>
-      <c r="O24" s="6"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R24" s="6"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C25" s="1">
         <v>279</v>
@@ -2312,40 +2367,40 @@
       <c r="E25" s="1">
         <v>267</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>0.04</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>0.1</v>
       </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1" t="s">
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N25" s="1">
+      <c r="Q25" s="1">
         <v>2021</v>
       </c>
-      <c r="O25" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R25" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
@@ -2356,38 +2411,38 @@
       <c r="E26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>0.04</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>0.5</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1" t="s">
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N26" s="1">
+      <c r="Q26" s="1">
         <v>2016</v>
       </c>
-      <c r="O26" s="6"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R26" s="6"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C27" s="3">
         <v>1920</v>
@@ -2398,43 +2453,44 @@
       <c r="E27" s="3">
         <v>1920</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
         <v>0.04</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <v>0.5</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <v>19</v>
       </c>
-      <c r="I27" s="1">
+      <c r="K27" s="1">
         <v>1.3</v>
       </c>
-      <c r="J27" s="1">
+      <c r="M27" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1" t="s">
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="1">
+      <c r="Q27" s="1">
         <v>2022</v>
       </c>
-      <c r="O27" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R27" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C28" s="1">
         <v>302</v>
@@ -2445,43 +2501,43 @@
       <c r="E28" s="1">
         <v>302</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <v>0.5</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I28" s="1">
+      <c r="K28" s="1">
         <v>0.2</v>
       </c>
-      <c r="J28" s="1">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1" t="s">
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M28" s="1">
+      <c r="P28" s="1">
         <v>2018</v>
       </c>
-      <c r="N28" s="1">
+      <c r="Q28" s="1">
         <v>2019</v>
       </c>
-      <c r="O28" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R28" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C29" s="1">
         <v>587</v>
@@ -2492,43 +2548,43 @@
       <c r="E29" s="1">
         <v>587</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>0.04</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>0.5</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <v>5.9</v>
       </c>
-      <c r="I29" s="1">
+      <c r="K29" s="1">
         <v>0.8</v>
       </c>
-      <c r="J29" s="1">
+      <c r="M29" s="1">
         <v>0.8</v>
       </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1" t="s">
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M29" s="1">
+      <c r="P29" s="1">
         <v>2012</v>
       </c>
-      <c r="N29" s="1">
+      <c r="Q29" s="1">
         <v>2020</v>
       </c>
-      <c r="O29" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R29" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1">
         <v>7</v>
@@ -2539,40 +2595,40 @@
       <c r="E30" s="1">
         <v>7</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
         <v>0.04</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>0.1</v>
       </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1" t="s">
+      <c r="K30" s="1">
         <v>0</v>
       </c>
       <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
         <v>2019</v>
       </c>
-      <c r="N30" s="1">
+      <c r="Q30" s="1">
         <v>2020</v>
       </c>
-      <c r="O30" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R30" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1">
         <v>349</v>
@@ -2583,43 +2639,43 @@
       <c r="E31" s="1">
         <v>349</v>
       </c>
-      <c r="F31" s="1">
+      <c r="G31" s="1">
         <v>0.04</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <v>0.5</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <v>3.5</v>
       </c>
-      <c r="I31" s="1">
+      <c r="K31" s="1">
         <v>0.4</v>
       </c>
-      <c r="J31" s="1">
+      <c r="M31" s="1">
         <v>0.2</v>
       </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1" t="s">
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M31" s="1">
+      <c r="P31" s="1">
         <v>2018</v>
       </c>
-      <c r="N31" s="1">
+      <c r="Q31" s="1">
         <v>2020</v>
       </c>
-      <c r="O31" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R31" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C32" s="3">
         <v>26880</v>
@@ -2630,41 +2686,41 @@
       <c r="E32" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F32" s="1">
+      <c r="G32" s="1">
         <v>0.04</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <v>0.5</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1" t="s">
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M32" s="1">
+      <c r="P32" s="1">
         <v>1990</v>
       </c>
-      <c r="N32" s="1">
+      <c r="Q32" s="1">
         <v>2018</v>
       </c>
-      <c r="O32" s="6"/>
-    </row>
-    <row r="33" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R32" s="6"/>
+    </row>
+    <row r="33" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C33" s="3">
         <v>1619</v>
@@ -2675,43 +2731,44 @@
       <c r="E33" s="3">
         <v>1250</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
         <v>0.04</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>0.5</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <v>13</v>
       </c>
-      <c r="I33" s="1">
+      <c r="K33" s="1">
         <v>5.6</v>
       </c>
-      <c r="J33" s="1">
+      <c r="M33" s="1">
         <v>5.6</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1" t="s">
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M33" s="1">
+      <c r="P33" s="1">
         <v>2019</v>
       </c>
-      <c r="N33" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q33" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C34" s="1">
         <v>890</v>
@@ -2722,43 +2779,43 @@
       <c r="E34" s="1">
         <v>610</v>
       </c>
-      <c r="F34" s="1">
+      <c r="G34" s="1">
         <v>0.04</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>0.5</v>
       </c>
-      <c r="H34" s="1">
+      <c r="I34" s="1">
         <v>6.1</v>
       </c>
-      <c r="I34" s="1">
+      <c r="K34" s="1">
         <v>7.4</v>
       </c>
-      <c r="J34" s="1">
+      <c r="M34" s="1">
         <v>7.4</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
         <v>2019</v>
       </c>
-      <c r="N34" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R34" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>6</v>
@@ -2766,43 +2823,43 @@
       <c r="E35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="1">
+      <c r="G35" s="1">
         <v>0.04</v>
       </c>
-      <c r="G35" s="1">
+      <c r="H35" s="1">
         <v>0.5</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="I35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I35" s="1">
+      <c r="K35" s="1">
         <v>22.2</v>
       </c>
-      <c r="J35" s="1">
+      <c r="M35" s="1">
         <v>22.2</v>
       </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1" t="s">
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M35" s="1">
+      <c r="P35" s="1">
         <v>1997</v>
       </c>
-      <c r="N35" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O35" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q35" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C36" s="3">
         <v>31046</v>
@@ -2813,152 +2870,152 @@
       <c r="E36" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F36" s="1">
+      <c r="G36" s="1">
         <v>0.04</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <v>0.5</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I36" s="1">
+      <c r="K36" s="1">
         <v>72</v>
       </c>
-      <c r="J36" s="1">
+      <c r="M36" s="1">
         <v>72</v>
       </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1">
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
         <v>1998</v>
       </c>
-      <c r="N36" s="1">
+      <c r="Q36" s="1">
         <v>2020</v>
       </c>
-      <c r="O36" s="6"/>
-    </row>
-    <row r="37" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R36" s="6"/>
+    </row>
+    <row r="37" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="1">
+      <c r="G37" s="1">
         <v>0.04</v>
       </c>
-      <c r="G37" s="1">
+      <c r="H37" s="1">
         <v>0.5</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I37" s="1">
+      <c r="K37" s="1">
         <v>0.4</v>
       </c>
-      <c r="J37" s="1">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
         <v>2008</v>
       </c>
-      <c r="N37" s="1">
+      <c r="Q37" s="1">
         <v>2020</v>
       </c>
-      <c r="O37" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R37" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F38" s="1">
+        <v>76</v>
+      </c>
+      <c r="G38" s="1">
         <v>0.04</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <v>0.5</v>
       </c>
-      <c r="I38" s="1">
+      <c r="K38" s="1">
         <v>37</v>
       </c>
-      <c r="J38" s="1">
+      <c r="M38" s="1">
         <v>37</v>
       </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1" t="s">
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M38" s="1">
+      <c r="P38" s="1">
         <v>2015</v>
       </c>
-      <c r="N38" s="1">
+      <c r="Q38" s="1">
         <v>2021</v>
       </c>
-      <c r="O38" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R38" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="1">
+        <v>76</v>
+      </c>
+      <c r="G39" s="1">
         <v>0.04</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <v>0.1</v>
       </c>
-      <c r="I39" s="1">
+      <c r="K39" s="1">
         <v>3.5</v>
       </c>
-      <c r="J39" s="1">
+      <c r="M39" s="1">
         <v>3.3</v>
       </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
         <v>2015</v>
       </c>
-      <c r="N39" s="1">
+      <c r="Q39" s="1">
         <v>2020</v>
       </c>
-      <c r="O39" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R39" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>6</v>
@@ -2966,38 +3023,38 @@
       <c r="E40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F40" s="1">
+      <c r="G40" s="1">
         <v>0.04</v>
       </c>
-      <c r="G40" s="1">
+      <c r="H40" s="1">
         <v>0.5</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40" s="1" t="s">
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N40" s="1">
+      <c r="Q40" s="1">
         <v>2013</v>
       </c>
-      <c r="O40" s="6"/>
-    </row>
-    <row r="41" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R40" s="6"/>
+    </row>
+    <row r="41" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>6</v>
@@ -3005,38 +3062,38 @@
       <c r="E41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F41" s="1">
+      <c r="G41" s="1">
         <v>0.04</v>
       </c>
-      <c r="G41" s="1">
+      <c r="H41" s="1">
         <v>0.5</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1" t="s">
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N41" s="1">
+      <c r="Q41" s="1">
         <v>2013</v>
       </c>
-      <c r="O41" s="6"/>
-    </row>
-    <row r="42" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R41" s="6"/>
+    </row>
+    <row r="42" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>6</v>
@@ -3044,38 +3101,38 @@
       <c r="E42" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F42" s="1">
+      <c r="G42" s="1">
         <v>0.04</v>
       </c>
-      <c r="G42" s="1">
+      <c r="H42" s="1">
         <v>0.5</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1" t="s">
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N42" s="1">
+      <c r="Q42" s="1">
         <v>2013</v>
       </c>
-      <c r="O42" s="6"/>
-    </row>
-    <row r="43" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R42" s="6"/>
+    </row>
+    <row r="43" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>6</v>
@@ -3083,38 +3140,38 @@
       <c r="E43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="1">
+      <c r="G43" s="1">
         <v>0.04</v>
       </c>
-      <c r="G43" s="1">
+      <c r="H43" s="1">
         <v>0.5</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="1">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N43" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O43" s="6"/>
-    </row>
-    <row r="44" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R43" s="6"/>
+    </row>
+    <row r="44" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C44" s="3">
         <v>1084</v>
@@ -3125,43 +3182,50 @@
       <c r="E44" s="3">
         <v>1007</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="3"/>
+      <c r="G44" s="1">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="G44" s="1">
+      <c r="H44" s="1">
         <v>0.1</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J44" s="1">
+      <c r="I44" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K44" s="1">
+        <v>5.82</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="M44" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="K44">
+      <c r="N44">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1" t="s">
+      <c r="O44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N44" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C45" s="3">
         <v>11278</v>
@@ -3172,119 +3236,120 @@
       <c r="E45" s="3">
         <v>7265</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="3"/>
+      <c r="G45" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G45" s="1">
+      <c r="H45" s="1">
         <v>0.5</v>
       </c>
-      <c r="H45" s="1">
+      <c r="I45" s="1">
         <v>127</v>
       </c>
-      <c r="I45" s="1">
+      <c r="K45" s="1">
         <v>27.09</v>
       </c>
-      <c r="J45" s="1">
+      <c r="M45" s="1">
         <v>8.39</v>
       </c>
-      <c r="K45">
+      <c r="N45">
         <v>0.18</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="O45" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="P45" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N45" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q45" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F46" s="1">
+      <c r="G46" s="1">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="G46" s="1">
+      <c r="H46" s="1">
         <v>0.5</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I46" s="1">
+      <c r="K46" s="1">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J46" s="1">
+      <c r="M46" s="1">
         <v>0.36</v>
       </c>
-      <c r="K46">
+      <c r="N46">
         <v>0.01</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M46" s="1" t="s">
+      <c r="O46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N46" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q46" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F47" s="1">
+        <v>76</v>
+      </c>
+      <c r="G47" s="1">
         <v>0.04</v>
       </c>
-      <c r="G47" s="1">
+      <c r="H47" s="1">
         <v>0.1</v>
       </c>
-      <c r="I47" s="1">
+      <c r="K47" s="1">
         <v>0.6</v>
       </c>
-      <c r="J47" s="1">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1">
         <v>2013</v>
       </c>
-      <c r="N47" s="1">
+      <c r="Q47" s="1">
         <v>2020</v>
       </c>
-      <c r="O47" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R47" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>6</v>
@@ -3292,38 +3357,38 @@
       <c r="E48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F48" s="1">
+      <c r="G48" s="1">
         <v>0.04</v>
       </c>
-      <c r="G48" s="1">
+      <c r="H48" s="1">
         <v>0.5</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I48" s="1">
-        <v>0</v>
-      </c>
-      <c r="J48" s="1">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48" s="1" t="s">
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N48" s="1">
+      <c r="Q48" s="1">
         <v>2018</v>
       </c>
-      <c r="O48" s="6"/>
-    </row>
-    <row r="49" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R48" s="6"/>
+    </row>
+    <row r="49" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C49" s="1">
         <v>31</v>
@@ -3334,40 +3399,40 @@
       <c r="E49" s="1">
         <v>26</v>
       </c>
-      <c r="F49" s="1">
+      <c r="G49" s="1">
         <v>0.04</v>
       </c>
-      <c r="G49" s="1">
+      <c r="H49" s="1">
         <v>0.1</v>
       </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49" s="1" t="s">
+      <c r="K49" s="1">
         <v>0</v>
       </c>
       <c r="M49" s="1">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P49" s="1">
         <v>2008</v>
       </c>
-      <c r="N49" s="1">
+      <c r="Q49" s="1">
         <v>2023</v>
       </c>
-      <c r="O49" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R49" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C50" s="3">
         <v>15227</v>
@@ -3378,34 +3443,35 @@
       <c r="E50" s="3">
         <v>13263</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="3"/>
+      <c r="G50" s="1">
         <v>0.04</v>
       </c>
-      <c r="G50" s="1">
+      <c r="H50" s="1">
         <v>0.5</v>
       </c>
-      <c r="H50" s="1">
+      <c r="I50" s="1">
         <v>133</v>
       </c>
-      <c r="I50" s="1">
+      <c r="K50" s="1">
         <v>57</v>
       </c>
-      <c r="J50" s="1">
-        <v>0</v>
-      </c>
-      <c r="K50">
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50">
         <v>57</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M50" s="1">
+      <c r="O50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
         <v>2019</v>
       </c>
-      <c r="N50" s="1">
+      <c r="Q50" s="1">
         <v>2023</v>
       </c>
-      <c r="O50" s="6"/>
+      <c r="R50" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
